--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>28.18426980551413</v>
+      </c>
+      <c r="C2">
         <v>29.98318474570894</v>
-      </c>
-      <c r="C2">
-        <v>28.18426980551413</v>
       </c>
       <c r="D2">
         <v>3.335202742741048</v>
       </c>
       <c r="E2">
-        <v>18.95660825470184</v>
+        <v>17.81925990114898</v>
       </c>
       <c r="F2">
         <v>63.22413184414918</v>
       </c>
       <c r="G2">
-        <v>17.81925990114898</v>
+        <v>18.95660825470184</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.43941980040454</v>
+      </c>
+      <c r="C3">
         <v>30.13004683143719</v>
-      </c>
-      <c r="C3">
-        <v>29.43941980040454</v>
       </c>
       <c r="D3">
         <v>3.318946052737683</v>
       </c>
       <c r="E3">
-        <v>18.8820878250807</v>
+        <v>18.44928132042146</v>
       </c>
       <c r="F3">
         <v>62.66863085449783</v>
       </c>
       <c r="G3">
-        <v>18.44928132042146</v>
+        <v>18.8820878250807</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.36657851655963</v>
+      </c>
+      <c r="C4">
         <v>37.38823825714645</v>
-      </c>
-      <c r="C4">
-        <v>29.36657851655963</v>
       </c>
       <c r="D4">
         <v>2.674637925227349</v>
       </c>
       <c r="E4">
-        <v>22.42108442833409</v>
+        <v>17.6106328349192</v>
       </c>
       <c r="F4">
         <v>59.96828273674672</v>
       </c>
       <c r="G4">
-        <v>17.6106328349192</v>
+        <v>22.42108442833409</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>38.76187126275062</v>
+      </c>
+      <c r="C5">
         <v>36.29968343299332</v>
-      </c>
-      <c r="C5">
-        <v>38.76187126275062</v>
       </c>
       <c r="D5">
         <v>2.75484496124031</v>
       </c>
       <c r="E5">
-        <v>20.73538276069922</v>
+        <v>22.14185252159936</v>
       </c>
       <c r="F5">
         <v>57.12276471770142</v>
       </c>
       <c r="G5">
-        <v>22.14185252159936</v>
+        <v>20.73538276069922</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.24471299093656</v>
+      </c>
+      <c r="C6">
         <v>38.27794561933535</v>
-      </c>
-      <c r="C6">
-        <v>29.24471299093656</v>
       </c>
       <c r="D6">
         <v>2.612470402525651</v>
       </c>
       <c r="E6">
-        <v>22.84941388638413</v>
+        <v>17.45716862037872</v>
       </c>
       <c r="F6">
         <v>59.69341749323714</v>
       </c>
       <c r="G6">
-        <v>17.45716862037872</v>
+        <v>22.84941388638413</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.14015528568585</v>
+      </c>
+      <c r="C7">
         <v>34.35695799323113</v>
-      </c>
-      <c r="C7">
-        <v>27.14015528568585</v>
       </c>
       <c r="D7">
         <v>2.910618571635521</v>
       </c>
       <c r="E7">
-        <v>21.27403846153846</v>
+        <v>16.80535009861933</v>
       </c>
       <c r="F7">
         <v>61.92061143984221</v>
       </c>
       <c r="G7">
-        <v>16.80535009861933</v>
+        <v>21.27403846153846</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.57477840829152</v>
+      </c>
+      <c r="C8">
         <v>37.79017961825259</v>
-      </c>
-      <c r="C8">
-        <v>28.57477840829152</v>
       </c>
       <c r="D8">
         <v>2.646190121618268</v>
       </c>
       <c r="E8">
-        <v>22.71522805434967</v>
+        <v>17.17595985792412</v>
       </c>
       <c r="F8">
         <v>60.10881208772623</v>
       </c>
       <c r="G8">
-        <v>17.17595985792412</v>
+        <v>22.71522805434967</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>26.00232906338379</v>
+      </c>
+      <c r="C9">
         <v>49.47596073864581</v>
-      </c>
-      <c r="C9">
-        <v>26.00232906338379</v>
       </c>
       <c r="D9">
         <v>2.021183591123067</v>
       </c>
       <c r="E9">
-        <v>28.194918467956</v>
+        <v>14.81797497155859</v>
       </c>
       <c r="F9">
         <v>56.98710656048539</v>
       </c>
       <c r="G9">
-        <v>14.81797497155859</v>
+        <v>28.194918467956</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.43441484661027</v>
+      </c>
+      <c r="C10">
         <v>36.59891427850019</v>
-      </c>
-      <c r="C10">
-        <v>29.43441484661027</v>
       </c>
       <c r="D10">
         <v>2.732321490169024</v>
       </c>
       <c r="E10">
-        <v>22.0431129528951</v>
+        <v>17.72801581568642</v>
       </c>
       <c r="F10">
         <v>60.22887123141847</v>
       </c>
       <c r="G10">
-        <v>17.72801581568642</v>
+        <v>22.0431129528951</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.7516708437761</v>
+      </c>
+      <c r="C11">
         <v>34.34106098579782</v>
-      </c>
-      <c r="C11">
-        <v>27.7516708437761</v>
       </c>
       <c r="D11">
         <v>2.911965941918808</v>
       </c>
       <c r="E11">
-        <v>21.18605849761629</v>
+        <v>17.12086071382554</v>
       </c>
       <c r="F11">
-        <v>61.69308078855818</v>
+        <v>61.69308078855817</v>
       </c>
       <c r="G11">
-        <v>17.12086071382554</v>
+        <v>21.18605849761628</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.32329830791451</v>
+      </c>
+      <c r="C12">
         <v>32.85322450277597</v>
-      </c>
-      <c r="C12">
-        <v>29.32329830791451</v>
       </c>
       <c r="D12">
         <v>3.043841251915786</v>
       </c>
       <c r="E12">
-        <v>20.25769447599128</v>
+        <v>18.08109940927995</v>
       </c>
       <c r="F12">
         <v>61.66120611472878</v>
       </c>
       <c r="G12">
-        <v>18.08109940927995</v>
+        <v>20.25769447599128</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>22.96655765376094</v>
+      </c>
+      <c r="C13">
         <v>44.92035024791645</v>
-      </c>
-      <c r="C13">
-        <v>22.96655765376094</v>
       </c>
       <c r="D13">
         <v>2.226162517613903</v>
       </c>
       <c r="E13">
-        <v>26.75631519416866</v>
+        <v>13.67977881110972</v>
       </c>
       <c r="F13">
         <v>59.56390599472164</v>
       </c>
       <c r="G13">
-        <v>13.67977881110972</v>
+        <v>26.75631519416866</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>29.25327553935573</v>
+      </c>
+      <c r="C14">
         <v>35.52851935769875</v>
-      </c>
-      <c r="C14">
-        <v>29.25327553935573</v>
       </c>
       <c r="D14">
         <v>2.814640232912796</v>
       </c>
       <c r="E14">
+        <v>17.75273509894183</v>
+      </c>
+      <c r="F14">
+        <v>60.68631553775333</v>
+      </c>
+      <c r="G14">
         <v>21.56094936330484</v>
-      </c>
-      <c r="F14">
-        <v>60.68631553775334</v>
-      </c>
-      <c r="G14">
-        <v>17.75273509894183</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.66031598513011</v>
+      </c>
+      <c r="C15">
         <v>38.17379182156134</v>
-      </c>
-      <c r="C15">
-        <v>27.66031598513011</v>
       </c>
       <c r="D15">
         <v>2.619598295800365</v>
       </c>
       <c r="E15">
-        <v>23.01926444833625</v>
+        <v>16.67950963222416</v>
       </c>
       <c r="F15">
         <v>60.30122591943957</v>
       </c>
       <c r="G15">
-        <v>16.67950963222416</v>
+        <v>23.01926444833625</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>22.29862475442043</v>
+      </c>
+      <c r="C16">
         <v>49.41060903732809</v>
-      </c>
-      <c r="C16">
-        <v>22.29862475442043</v>
       </c>
       <c r="D16">
         <v>2.023856858846918</v>
       </c>
       <c r="E16">
+        <v>12.98627002288329</v>
+      </c>
+      <c r="F16">
+        <v>58.23798627002289</v>
+      </c>
+      <c r="G16">
         <v>28.77574370709382</v>
-      </c>
-      <c r="F16">
-        <v>58.23798627002288</v>
-      </c>
-      <c r="G16">
-        <v>12.98627002288329</v>
       </c>
     </row>
   </sheetData>
